--- a/data/statistics/international_statistics_new.xlsx
+++ b/data/statistics/international_statistics_new.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,6 +546,50 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>38.37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>chanhua</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>世纪云芯</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>XJ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BM1374PA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Y31010552</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>5641</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SZK202605210001</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>38.37</v>
       </c>
     </row>

--- a/data/statistics/international_statistics_new.xlsx
+++ b/data/statistics/international_statistics_new.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,7 +524,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>深圳前海仓</t>
+          <t>深圳前海保税区</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -546,50 +546,6 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>38.37</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>chanhua</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>世纪云芯</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>XJ</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BM1374PA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Y31010552</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>5641</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>SZK202605210001</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="n">
         <v>38.37</v>
       </c>
     </row>
